--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24940.85</v>
+        <v>24804.53</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>73763.16</v>
+        <v>73669.27</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>48734.55</v>
+        <v>48894.85</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>27801.71</v>
+        <v>27442.36</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42607.59</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>35642.99</v>
+        <v>35190.25</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>27004.04</v>
+        <v>26661.03</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>56753.94</v>
+        <v>56189.26</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>145686.06</v>
+        <v>145163.66</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>37396.5</v>
+        <v>36963.71</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>54008.07</v>
+        <v>53550.58</v>
       </c>
     </row>
     <row r="13">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25472.64</v>
+        <v>25540.19</v>
       </c>
     </row>
     <row r="14">
@@ -1305,7 +1305,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35642.99</v>
+        <v>35888.33</v>
       </c>
     </row>
     <row r="15">
@@ -1366,7 +1366,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37396.5</v>
+        <v>37797.64</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>35319.24</v>
+        <v>35097.92</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>33770.56</v>
+        <v>34005.68</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>68209.44</v>
+        <v>68816.96000000001</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>29547.92</v>
+        <v>29387.01</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>51536.01</v>
+        <v>51337.1</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>36619.68</v>
+        <v>36764.06</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>48318.64</v>
+        <v>47977.65</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>20822.21</v>
+        <v>20821.14</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>38184.46</v>
+        <v>38217.35</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>35594.33</v>
+        <v>35183.42</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>24592.73</v>
+        <v>24451.47</v>
       </c>
     </row>
     <row r="27">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>67563.55</v>
+        <v>66109.92</v>
       </c>
     </row>
     <row r="28">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>29450.27</v>
+        <v>28511.19</v>
       </c>
     </row>
     <row r="29">
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>126768.29</v>
+        <v>123430.06</v>
       </c>
     </row>
     <row r="30">
@@ -2285,7 +2285,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>30285.23</v>
+        <v>30629.64</v>
       </c>
     </row>
     <row r="31">
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>36254.69</v>
+        <v>36404.96</v>
       </c>
     </row>
     <row r="32">
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>36720.14</v>
+        <v>36796.21</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>25640.39</v>
+        <v>25831.41</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>38805.41</v>
+        <v>38418.41</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>33856.08</v>
+        <v>33772.48</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>69895.17</v>
+        <v>70715.08</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>36838.4</v>
+        <v>37270.54</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>18247.8</v>
+        <v>18461.86</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>23470.22</v>
+        <v>23867.16</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>72186.33</v>
+        <v>71161.84</v>
       </c>
     </row>
     <row r="41">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>27078.35</v>
+        <v>26694.05</v>
       </c>
     </row>
     <row r="42">
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>72690.97</v>
+        <v>71659.32000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3078,7 +3078,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>18297.73</v>
+        <v>18046.32</v>
       </c>
     </row>
     <row r="44">
@@ -3139,7 +3139,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>32364.52</v>
+        <v>32163.87</v>
       </c>
     </row>
     <row r="45">
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>70315.81</v>
+        <v>70635.16</v>
       </c>
     </row>
     <row r="46">
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>39122.88</v>
+        <v>39243.84</v>
       </c>
     </row>
     <row r="47">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>29634.47</v>
+        <v>29726.08</v>
       </c>
     </row>
     <row r="48">
@@ -3383,7 +3383,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>11800.4</v>
+        <v>11625.57</v>
       </c>
     </row>
     <row r="49">
@@ -3444,7 +3444,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>396.28</v>
+        <v>390.41</v>
       </c>
     </row>
     <row r="50">
@@ -3505,7 +3505,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>25477.3</v>
+        <v>25099.83</v>
       </c>
     </row>
     <row r="51">
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1444</v>
+        <v>1422.6</v>
       </c>
     </row>
     <row r="52">
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>18411.12</v>
+        <v>18595.48</v>
       </c>
     </row>
     <row r="53">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>72361.03999999999</v>
+        <v>72526.98</v>
       </c>
     </row>
     <row r="54">
@@ -3753,7 +3753,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22095.45</v>
+        <v>22025.65</v>
       </c>
     </row>
     <row r="55">
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17244.69</v>
+        <v>17210.12</v>
       </c>
     </row>
     <row r="56">
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>398.55</v>
+        <v>397.75</v>
       </c>
     </row>
     <row r="57">
@@ -3936,7 +3936,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>35561.57</v>
+        <v>34987.69</v>
       </c>
     </row>
     <row r="58">
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>721.13</v>
+        <v>709.49</v>
       </c>
     </row>
     <row r="59">
@@ -4058,7 +4058,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>26853.71</v>
+        <v>26541.25</v>
       </c>
     </row>
     <row r="60">
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>33732.67</v>
+        <v>33566.81</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M60"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3882-379-CM25</t>
+          <t>4686-581-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>PIAMONTE S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.642.160-6</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24804.53</v>
+        <v>43297.98</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2920-286-CM25</t>
+          <t>707419-177-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +585,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>73669.27</v>
+        <v>32724.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4077-106-CM25</t>
+          <t>1208983-186-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>48894.85</v>
+        <v>39797.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2424-2573-CM25</t>
+          <t>3882-379-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>69.060.400-0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>27442.36</v>
+        <v>24804.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3275-4234-CM25</t>
+          <t>2920-286-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>42056.86</v>
+        <v>73669.27</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2694-425-CM25</t>
+          <t>4077-106-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>V ZONA CARABINEROS VALPARAISO</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>35190.25</v>
+        <v>48894.85</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2694-426-CM25</t>
+          <t>2424-2573-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.000-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>26661.03</v>
+        <v>27442.36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3624-632-CM25</t>
+          <t>3275-4234-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cecor S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.010.151-6</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>56189.26</v>
+        <v>42056.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2780-547-CM25</t>
+          <t>2694-425-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,32 +1042,28 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>145163.66</v>
+        <v>35190.25</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2783-938-CM25</t>
+          <t>2694-426-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1082,22 +1078,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>36963.71</v>
+        <v>26661.03</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>643-304-CM25</t>
+          <t>3624-632-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,22 +1139,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.817.000-4</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Cecor S.A.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.010.151-6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>53550.58</v>
+        <v>56189.26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>643-317-CM25</t>
+          <t>2780-547-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,22 +1200,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.817.000-4</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1229,28 +1225,32 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>25540.19</v>
+        <v>145163.66</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2757-951-CM25</t>
+          <t>2783-938-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1290,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>35888.33</v>
+        <v>36963.71</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2427-1541-CM25</t>
+          <t>643-304-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,22 +1326,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>61.817.000-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>37797.64</v>
+        <v>53550.58</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3820-41-CM26</t>
+          <t>643-317-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,27 +1382,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>61.817.000-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1427,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>35097.92</v>
+        <v>25540.19</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3775-13-CM26</t>
+          <t>2757-951-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>34005.68</v>
+        <v>35888.33</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3820-123-CM26</t>
+          <t>2427-1541-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,27 +1504,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1549,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>68816.96000000001</v>
+        <v>37797.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3820-139-CM26</t>
+          <t>3820-41-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,17 +1565,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1610,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>29387.01</v>
+        <v>35097.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3661-133-CM26</t>
+          <t>3775-13-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1671,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>51337.1</v>
+        <v>34005.68</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3775-20-CM26</t>
+          <t>3820-123-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1732,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>36764.06</v>
+        <v>68816.96000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1431841-99-CM26</t>
+          <t>3820-139-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,27 +1748,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1778,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1793,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>47977.65</v>
+        <v>29387.01</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2464-304-CM26</t>
+          <t>3661-133-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.060.100-1</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>20821.14</v>
+        <v>51337.1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2697-1-CM26</t>
+          <t>3775-20-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>38217.35</v>
+        <v>36764.06</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>859378-76-CM26</t>
+          <t>1431841-99-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1946,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>69.254.800-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>Automotriz Tecnosur Limitada</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.585.230-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>35183.42</v>
+        <v>47977.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3232-192-CM26</t>
+          <t>2464-304-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.060.100-1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>24451.47</v>
+        <v>20821.14</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>701-160-CM26</t>
+          <t>2697-1-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2058,22 +2058,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>PIAMONTE S A</t>
+          <t>Automotriz Tecnosur Limitada</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>96.642.160-6</t>
+          <t>78.585.230-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,28 +2098,28 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>66109.92</v>
+        <v>38217.35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3515-155-CM26</t>
+          <t>859378-76-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,43 +2159,43 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>28511.19</v>
+        <v>35183.42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3624-159-CM26</t>
+          <t>3232-192-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,62 +2205,58 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>123430.06</v>
+        <v>24451.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3632-35-CM26</t>
+          <t>701-160-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2270,12 +2266,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>PIAMONTE S A</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.642.160-6</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2285,13 +2281,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>30629.64</v>
+        <v>66109.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1048-167-CM26</t>
+          <t>3515-155-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2306,22 +2302,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2331,12 +2327,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2346,13 +2342,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>36404.96</v>
+        <v>28511.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3035-175-CM26</t>
+          <t>3624-159-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2367,22 +2363,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2392,28 +2388,32 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>36796.21</v>
+        <v>123430.06</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2464-605-CM26</t>
+          <t>3632-35-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2423,27 +2423,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.060.100-1</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>25831.41</v>
+        <v>30629.64</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3134-100-CM26</t>
+          <t>1048-167-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2529,13 +2529,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>38418.41</v>
+        <v>36404.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>377-204-CM26</t>
+          <t>3035-175-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2545,27 +2545,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2590,13 +2590,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>33772.48</v>
+        <v>36796.21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>586-215-CM26</t>
+          <t>2464-605-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>69.060.100-1</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>70715.08</v>
+        <v>25831.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1048-223-CM26</t>
+          <t>3134-100-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>84.807.200-1</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2712,13 +2712,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>37270.54</v>
+        <v>38418.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>3561-226-CM26</t>
+          <t>377-204-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2773,13 +2773,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>18461.86</v>
+        <v>33772.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>3661-311-CM26</t>
+          <t>586-215-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>60.804.000-5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2834,13 +2834,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>23867.16</v>
+        <v>70715.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3678-155-CM26</t>
+          <t>1048-223-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2855,22 +2855,22 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2895,13 +2895,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>71161.84</v>
+        <v>37270.54</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3624-311-CM26</t>
+          <t>3561-226-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2956,13 +2956,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>26694.05</v>
+        <v>18461.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3624-312-CM26</t>
+          <t>3661-311-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3017,13 +3017,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>71659.32000000001</v>
+        <v>23867.16</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3117-778-CM26</t>
+          <t>3678-155-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3038,22 +3038,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>18046.32</v>
+        <v>71161.84</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3820-514-CM26</t>
+          <t>3624-311-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3099,22 +3099,22 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3139,13 +3139,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>32163.87</v>
+        <v>26694.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3820-518-CM26</t>
+          <t>3624-312-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3160,22 +3160,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>70635.16</v>
+        <v>71659.32000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3515-285-CM26</t>
+          <t>3117-778-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3221,22 +3221,22 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3261,13 +3261,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>39243.84</v>
+        <v>18046.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3693-105-CM26</t>
+          <t>3820-514-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3282,22 +3282,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>GUILLERMO MORALES GROUP LIMITADA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>78.027.627-4</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3322,13 +3322,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>29726.08</v>
+        <v>32163.87</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3661-357-CM26</t>
+          <t>3820-518-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3343,7 +3343,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3353,12 +3353,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3383,13 +3383,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>11625.57</v>
+        <v>70635.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3661-358-CM26</t>
+          <t>3693-105-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>GUILLERMO MORALES GROUP LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>78.027.627-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3444,13 +3444,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>390.41</v>
+        <v>29726.08</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1456836-6-CM26</t>
+          <t>3515-285-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.981.410-K</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3505,13 +3505,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>25099.83</v>
+        <v>39243.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1456836-7-CM26</t>
+          <t>3661-357-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3531,17 +3531,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.981.410-K</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3566,13 +3566,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1422.6</v>
+        <v>11625.57</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3624-359-CM26</t>
+          <t>3661-358-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>77.461.290-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3627,13 +3627,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>18595.48</v>
+        <v>390.41</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2697-8-CM26</t>
+          <t>1456836-6-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.981.410-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3673,32 +3673,28 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
-        </is>
-      </c>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>72526.98</v>
+        <v>25099.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>377-310-CM26</t>
+          <t>1456836-7-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3708,12 +3704,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3723,12 +3719,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.981.410-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3738,12 +3734,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3753,13 +3749,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>22025.65</v>
+        <v>1422.6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3820-637-CM26</t>
+          <t>3624-359-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3774,22 +3770,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3799,12 +3795,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3814,13 +3810,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>17210.12</v>
+        <v>18595.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3820-638-CM26</t>
+          <t>2697-8-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3835,22 +3831,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3860,28 +3856,32 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Antofagasta </t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>397.75</v>
+        <v>72526.98</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2688-236-CM26</t>
+          <t>377-310-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3921,12 +3921,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3936,13 +3936,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>34987.69</v>
+        <v>22025.65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2688-237-CM26</t>
+          <t>3820-637-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3957,22 +3957,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3997,13 +3997,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>709.49</v>
+        <v>17210.12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1195104-212-CM26</t>
+          <t>3820-638-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4028,12 +4028,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>62.000.920-2</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4043,12 +4043,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>26541.25</v>
+        <v>397.75</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2780-248-CM26</t>
+          <t>2688-236-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4079,7 +4079,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4119,6 +4119,189 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
+        <v>34987.69</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2688-237-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>69.061.600-9</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>709.49</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>1195104-212-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>62.000.920-2</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>26541.25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2780-248-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>69.050.100-7</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
         <v>33566.81</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Valparaíso" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4686-581-CM25</t>
+          <t>1305543-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>61.981.050-3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE MARGA MARGA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>PIAMONTE S A</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.642.160-6</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>43297.98</v>
+        <v>23903.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>707419-177-CM25</t>
+          <t>2755-1-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-10-10</t>
+          <t>2025-01-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>32724.78</v>
+        <v>38523.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1208983-186-CM25</t>
+          <t>2780-12-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,27 +646,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>39797.26</v>
+        <v>37402.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3882-379-CM25</t>
+          <t>3073-31-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.060.400-0</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>24804.53</v>
+        <v>33126</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2920-286-CM25</t>
+          <t>1305525-3-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.252.300-8</t>
+          <t>61.981.120-8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE COSTA CENTRAL</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>73669.27</v>
+        <v>24149.6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4077-106-CM25</t>
+          <t>3015-17-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,27 +829,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.979.360-9</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>48894.85</v>
+        <v>29452.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2424-2573-CM25</t>
+          <t>4373-10-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.061.000-0</t>
+          <t>60.511.053-3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>27442.36</v>
+        <v>12419.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3275-4234-CM25</t>
+          <t>3675-8-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>42056.86</v>
+        <v>25004.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2694-425-CM25</t>
+          <t>4373-21-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>60.511.053-3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>35190.25</v>
+        <v>12153.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2694-426-CM25</t>
+          <t>2920-35-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.252.300-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>26661.03</v>
+        <v>25336.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3624-632-CM25</t>
+          <t>3679-56-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-02-25</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Cecor S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.010.151-6</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>56189.26</v>
+        <v>38566.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2780-547-CM25</t>
+          <t>1048-102-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,27 +1195,27 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,32 +1225,28 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>145163.66</v>
+        <v>25906.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2783-938-CM25</t>
+          <t>2427-188-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1256,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1290,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>DERCOMAQ SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>96.545.450-0</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>36963.71</v>
+        <v>22732.61</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>643-304-CM25</t>
+          <t>3515-149-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1321,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-03-04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.817.000-4</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>53550.58</v>
+        <v>10096.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>643-317-CM25</t>
+          <t>1725-4478-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,27 +1378,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.817.000-4</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1427,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>25540.19</v>
+        <v>54174.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2757-951-CM25</t>
+          <t>3678-63-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,27 +1439,27 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1473,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1488,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>35888.33</v>
+        <v>36974.67</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2427-1541-CM25</t>
+          <t>3678-64-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1504,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1519,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.050.500-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1534,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>COMERCIAL ANFRUNS Y COMPANIA SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.385.500-4</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1549,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>37797.64</v>
+        <v>35123.79</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3820-41-CM26</t>
+          <t>3138-17-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1565,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>61.953.100-0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1595,12 +1591,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1610,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>35097.92</v>
+        <v>61000.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3775-13-CM26</t>
+          <t>3134-51-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1626,12 +1622,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1641,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1656,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1671,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>34005.68</v>
+        <v>31770.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3820-123-CM26</t>
+          <t>3134-57-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1687,12 +1683,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1702,12 +1698,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1717,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1732,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>68816.96000000001</v>
+        <v>34786.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3820-139-CM26</t>
+          <t>2755-117-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1748,27 +1744,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1778,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1793,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>29387.01</v>
+        <v>23549.04</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3661-133-CM26</t>
+          <t>3035-100-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1809,12 +1805,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1824,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1839,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1854,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>51337.1</v>
+        <v>30038.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3775-20-CM26</t>
+          <t>1725-4607-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1870,12 +1866,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2025-04-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1885,12 +1881,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1900,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1915,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>36764.06</v>
+        <v>34214.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1431841-99-CM26</t>
+          <t>2780-129-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,12 +1927,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1946,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1961,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1976,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>47977.65</v>
+        <v>20591.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2464-304-CM26</t>
+          <t>3632-43-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1992,27 +1988,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.060.100-1</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2022,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>20821.14</v>
+        <v>26486.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2697-1-CM26</t>
+          <t>4412-21-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2053,12 +2049,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-04-17</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2068,12 +2064,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2083,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>38217.35</v>
+        <v>33525.73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>859378-76-CM26</t>
+          <t>4412-22-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2114,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2129,12 +2125,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2144,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>35183.42</v>
+        <v>33571.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3232-192-CM26</t>
+          <t>3596-341-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2175,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2025-04-25</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2190,12 +2186,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2205,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2220,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>24451.47</v>
+        <v>23525.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>701-160-CM26</t>
+          <t>2464-504-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2236,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2025-04-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2251,12 +2247,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>69.060.100-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2266,12 +2262,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>PIAMONTE S A</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.642.160-6</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2281,43 +2277,43 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>66109.92</v>
+        <v>35002.86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>3515-155-CM26</t>
+          <t>2694-111-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2025-05-13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2327,12 +2323,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2342,43 +2338,43 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>28511.19</v>
+        <v>15350.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3624-159-CM26</t>
+          <t>643-176-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>61.817.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2388,47 +2384,43 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.141.853-k</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>123430.06</v>
+        <v>28990.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3632-35-CM26</t>
+          <t>640840-82-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2438,12 +2430,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2453,12 +2445,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2468,28 +2460,28 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>30629.64</v>
+        <v>27363.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1048-167-CM26</t>
+          <t>3035-216-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2499,12 +2491,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2514,12 +2506,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2529,28 +2521,28 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>36404.96</v>
+        <v>28143.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>3035-175-CM26</t>
+          <t>1725-4794-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2560,12 +2552,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2575,58 +2567,62 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>36796.21</v>
+        <v>233767.46</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2464-605-CM26</t>
+          <t>2780-209-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2025-06-11</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.060.100-1</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2636,12 +2632,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2651,43 +2647,43 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>25831.41</v>
+        <v>17099.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>3134-100-CM26</t>
+          <t>3820-309-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2697,12 +2693,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2712,28 +2708,28 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>38418.41</v>
+        <v>34588.24</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>377-204-CM26</t>
+          <t>4412-27-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2743,12 +2739,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.061.300-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I. MUNICIPALIDAD DE QUILPUE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2758,58 +2754,62 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>33772.48</v>
+        <v>106649.21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>586-215-CM26</t>
+          <t>4439-9-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>60.804.000-5</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2834,43 +2834,43 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>70715.08</v>
+        <v>26073.37</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1048-223-CM26</t>
+          <t>3561-451-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2880,12 +2880,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2895,28 +2895,28 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>37270.54</v>
+        <v>28056.43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>3561-226-CM26</t>
+          <t>4290-82-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.061.100-7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2956,43 +2956,43 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>18461.86</v>
+        <v>34257.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>3661-311-CM26</t>
+          <t>3624-376-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3002,12 +3002,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3017,43 +3017,43 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>23867.16</v>
+        <v>34076.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>3678-155-CM26</t>
+          <t>3138-104-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>69.050.500-2</t>
+          <t>61.953.100-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PETORCA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3078,28 +3078,28 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>71161.84</v>
+        <v>71526.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3624-311-CM26</t>
+          <t>3445-263-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.051.300-5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE RINCONADA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3139,43 +3139,43 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>26694.05</v>
+        <v>28527.57</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3624-312-CM26</t>
+          <t>3134-279-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-08-08</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3200,28 +3200,28 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>71659.32000000001</v>
+        <v>19578.65</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>3117-778-CM26</t>
+          <t>3134-293-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3231,12 +3231,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.102.006-6</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3261,28 +3261,28 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>18046.32</v>
+        <v>32858.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3820-514-CM26</t>
+          <t>3134-301-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3292,12 +3292,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3322,43 +3322,43 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>32163.87</v>
+        <v>51271.63</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>3820-518-CM26</t>
+          <t>4469-750-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3383,43 +3383,43 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>70635.16</v>
+        <v>27107.25</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3693-105-CM26</t>
+          <t>2427-906-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>GUILLERMO MORALES GROUP LIMITADA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>78.027.627-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3444,43 +3444,43 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>29726.08</v>
+        <v>70825.84</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3515-285-CM26</t>
+          <t>1298708-54-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>65.218.135-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>CORPORACIÓN MUNICIPAL DE ADMINISTRACIÓN SITIO PATRIMONIO MUNDIAL ÁREA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3505,28 +3505,28 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>39243.84</v>
+        <v>27998.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>3661-357-CM26</t>
+          <t>2694-281-CM25</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3566,43 +3566,43 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>11625.57</v>
+        <v>30627.67</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>3661-358-CM26</t>
+          <t>1048-403-CM25</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -3612,12 +3612,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>77.461.290-4</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3627,28 +3627,28 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>390.41</v>
+        <v>26357.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1456836-6-CM26</t>
+          <t>4686-581-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.981.410-K</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3673,12 +3673,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>PIAMONTE S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>96.642.160-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3688,43 +3688,43 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>25099.83</v>
+        <v>43297.98</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1456836-7-CM26</t>
+          <t>3117-1264-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.981.410-K</t>
+          <t>61.102.006-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3734,12 +3734,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3749,43 +3749,43 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1422.6</v>
+        <v>20680.66</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>3624-359-CM26</t>
+          <t>2698-188-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ CORDILLERA S.A.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.853.470-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3810,43 +3810,43 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>18595.48</v>
+        <v>37360.86</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2697-8-CM26</t>
+          <t>3134-349-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3856,62 +3856,58 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
-        </is>
-      </c>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>72526.98</v>
+        <v>22423.43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>377-310-CM26</t>
+          <t>2803-324-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3921,12 +3917,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3936,43 +3932,43 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>22025.65</v>
+        <v>33628.26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>3820-637-CM26</t>
+          <t>707419-177-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3982,12 +3978,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3997,28 +3993,28 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>17210.12</v>
+        <v>32724.78</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3820-638-CM26</t>
+          <t>3232-578-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4028,12 +4024,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4043,12 +4039,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4058,43 +4054,43 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>397.75</v>
+        <v>23366.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2688-236-CM26</t>
+          <t>3134-379-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4104,12 +4100,12 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>96.928.530-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4119,43 +4115,43 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>34987.69</v>
+        <v>32677.52</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2688-237-CM26</t>
+          <t>2737-661-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4165,12 +4161,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.141.853-k</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4180,28 +4176,28 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>709.49</v>
+        <v>57140.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1195104-212-CM26</t>
+          <t>1080157-124-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4211,12 +4207,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>62.000.920-2</t>
+          <t>61.979.360-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4226,12 +4222,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4241,43 +4237,43 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>26541.25</v>
+        <v>49470.76</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2780-248-CM26</t>
+          <t>1208983-186-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4287,12 +4283,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4302,7 +4298,3923 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
+        <v>39797.26</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1248381-42-CM25</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025-10-29</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>75.067.200-0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>CORPORACION MUNICIPAL DE ISLA DE PASCUA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>27513.45</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>3882-379-CM25</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>69.060.400-0</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LLAY LLAY</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>24804.53</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2920-286-CM25</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>69.252.300-8</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE JUAN FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>73669.27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>4077-106-CM25</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>nov-2025</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.979.360-9</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>V ZONA CARABINEROS VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>48894.85</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2424-2573-CM25</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>69.061.000-0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VINA DEL MAR</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>27442.36</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3275-4234-CM25</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60.506.000-5</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>42056.86</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2694-425-CM25</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>69.073.600-4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>35190.25</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2694-426-CM25</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>69.073.600-4</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>26661.03</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>3624-632-CM25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025-12-03</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>69.060.600-3</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Cecor S.A.</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.010.151-6</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>56189.26</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2780-547-CM25</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>69.050.100-7</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>145163.66</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2783-938-CM25</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>69.050.100-7</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>36963.71</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>643-304-CM25</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.817.000-4</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>53550.58</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>643-317-CM25</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.817.000-4</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>25540.19</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2757-951-CM25</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025-12-22</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>69.073.400-1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>35888.33</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2427-1541-CM25</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025-12-24</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>69.060.900-2</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>78.098.600-K</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>37797.64</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>3820-41-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-01-21</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>69.051.000-6</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>35097.92</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>3775-13-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>69.060.500-7</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>34005.68</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>3820-123-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>69.051.000-6</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>96.918.300-5</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>68816.96000000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>3820-139-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>69.051.000-6</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>29387.01</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>3661-133-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>69.051.400-1</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>51337.1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>3775-20-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>69.060.500-7</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>36764.06</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1431841-99-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>69.254.800-0</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>MUNICIPALIDAD DE RECOLETA</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Automotriz Tecnosur Limitada</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>78.585.230-3</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>47977.65</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2464-304-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>69.060.100-1</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>20821.14</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2697-1-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>69.073.600-4</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Automotriz Tecnosur Limitada</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>78.585.230-3</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>38217.35</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>859378-76-CM26</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>35183.42</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>3232-192-CM26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>69.073.500-8</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>24451.47</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>701-160-CM26</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>PIAMONTE S A</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>96.642.160-6</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>66109.92</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>3515-155-CM26</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>69.060.300-4</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>28511.19</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>3624-159-CM26</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>69.060.600-3</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>76.141.853-k</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>123430.06</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>3632-35-CM26</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>69.060.600-3</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>30629.64</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>1048-167-CM26</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>69.073.700-0</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>36404.96</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>3035-175-CM26</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>69.060.200-8</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>36796.21</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2464-605-CM26</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>69.060.100-1</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>25831.41</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>3134-100-CM26</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>61.102.014-7</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>38418.41</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>377-204-CM26</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>69.061.600-9</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>33772.48</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>586-215-CM26</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>60.804.000-5</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>70715.08</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>1048-223-CM26</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>69.073.700-0</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="n">
+        <v>37270.54</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>3561-226-CM26</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>69.060.300-4</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="n">
+        <v>18461.86</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>3661-311-CM26</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>69.051.400-1</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>77.461.290-4</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="n">
+        <v>23867.16</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>3678-155-CM26</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>69.050.500-2</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PETORCA</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="n">
+        <v>71161.84</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>3624-311-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>69.060.600-3</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>79.649.140-k</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>26694.05</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>3624-312-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>69.060.600-3</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>71659.32000000001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>3117-778-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>61.102.006-6</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>18046.32</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>3820-514-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>69.051.000-6</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>32163.87</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>3820-518-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>69.051.000-6</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>70635.16</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>3693-105-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>69.061.700-5</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>GUILLERMO MORALES GROUP LIMITADA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>78.027.627-4</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>29726.08</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>3515-285-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>69.060.300-4</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>POMPEYO CARRASCO SPA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>81.318.700-0</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>39243.84</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>3661-357-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>69.051.400-1</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>77.461.290-4</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>11625.57</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>3661-358-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>69.051.400-1</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>CARFLEX SERVICIOS FINANCIEROS S.A.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>77.461.290-4</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>390.41</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1456836-6-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>61.981.410-K</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>25099.83</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1456836-7-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>61.981.410-K</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>1422.6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>3624-359-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>69.060.600-3</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>18595.48</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2697-8-CM26</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>69.073.600-4</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>72526.98</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>377-310-CM26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>69.061.600-9</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>22025.65</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>3820-637-CM26</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>69.051.000-6</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>17210.12</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>3820-638-CM26</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>69.051.000-6</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>SUMMIT STORE SPA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="n">
+        <v>397.75</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2688-236-CM26</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>69.061.600-9</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="n">
+        <v>34987.69</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2688-237-CM26</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>69.061.600-9</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="n">
+        <v>709.49</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>1195104-212-CM26</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>62.000.920-2</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="n">
+        <v>26541.25</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2780-248-CM26</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>69.050.100-7</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="n">
         <v>33566.81</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>1456835-12-CM26</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>61.981.430-4</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="n">
+        <v>27051.14</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>640840-148-CM26</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>69.060.700-k</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>37712.43</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>4844-60-CM26</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>69.073.700-0</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>71799.47</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>4844-61-CM26</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>69.073.700-0</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>SUMMIT MOTORS S.A.</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="n">
+        <v>2964.74</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M127"/>
+  <dimension ref="A1:M130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4243,7 +4243,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1208983-186-CM25</t>
+          <t>1248381-42-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>75.067.200-0</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CORPORACION MUNICIPAL DE ISLA DE PASCUA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4298,13 +4298,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>39797.26</v>
+        <v>27513.45</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1248381-42-CM25</t>
+          <t>1208983-186-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4324,17 +4324,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>75.067.200-0</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE ISLA DE PASCUA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>27513.45</v>
+        <v>39797.26</v>
       </c>
     </row>
     <row r="65">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>V ZONA CARABINEROS VALPARAISO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5040,7 +5040,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>643-317-CM25</t>
+          <t>1375753-101-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.817.000-4</t>
+          <t>61.981.290-5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA LOS ANDES</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>25540.19</v>
+        <v>25974.31</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2757-951-CM25</t>
+          <t>643-317-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.073.400-1</t>
+          <t>61.817.000-4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5156,13 +5156,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>35888.33</v>
+        <v>25540.19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2427-1541-CM25</t>
+          <t>2757-951-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5177,22 +5177,22 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>69.060.900-2</t>
+          <t>69.073.400-1</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALPARAISO</t>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5202,12 +5202,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>MARCELO FRONZA Y CIA LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>78.098.600-K</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5217,13 +5217,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>37797.64</v>
+        <v>35888.33</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3820-41-CM26</t>
+          <t>2427-1541-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.060.900-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5263,12 +5263,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>MARCELO FRONZA Y CIA LTDA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>78.098.600-K</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5278,13 +5278,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>35097.92</v>
+        <v>37797.64</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3775-13-CM26</t>
+          <t>3820-41-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5294,27 +5294,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5339,13 +5339,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>34005.68</v>
+        <v>35097.92</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3820-123-CM26</t>
+          <t>3775-13-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -5385,12 +5385,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.918.300-5</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>68816.96000000001</v>
+        <v>34005.68</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3820-139-CM26</t>
+          <t>3820-123-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>DIFOR CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>96.918.300-5</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5461,13 +5461,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>29387.01</v>
+        <v>68816.96000000001</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3661-133-CM26</t>
+          <t>3820-139-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5492,12 +5492,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.051.400-1</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5522,13 +5522,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>51337.1</v>
+        <v>29387.01</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3775-20-CM26</t>
+          <t>3661-133-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>69.060.500-7</t>
+          <t>69.051.400-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE HIJUELAS</t>
+          <t>I MUNICIPALIDAD DE SAN ESTEBAN</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
@@ -5583,13 +5583,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>36764.06</v>
+        <v>51337.1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1431841-99-CM26</t>
+          <t>3775-20-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5604,22 +5604,22 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.254.800-0</t>
+          <t>69.060.500-7</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE HIJUELAS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5629,12 +5629,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>78.585.230-3</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>47977.65</v>
+        <v>36764.06</v>
       </c>
     </row>
     <row r="86">
@@ -5751,7 +5751,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Automotriz Tecnosur Limitada</t>
+          <t>AUTOMOTRIZ TECNOSUR LIMITADA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>INCHCAPE CAMIONES Y BUSES CHILE S.A.</t>
+          <t>Inchcape Camiones y Buses Chile S.A.</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DEL TERRITORIO MARITIMO Y M.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRUNO FRITSCH S.A. </t>
+          <t>BRUNO FRITSCH S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -6904,7 +6904,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO DE BIENESTAR SOCIAL 1° Z.N.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7057,7 +7057,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3693-105-CM26</t>
+          <t>3515-285-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.061.700-5</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL QUISCO</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7097,12 +7097,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>GUILLERMO MORALES GROUP LIMITADA</t>
+          <t>POMPEYO CARRASCO SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>78.027.627-4</t>
+          <t>81.318.700-0</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7112,13 +7112,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>29726.08</v>
+        <v>39243.84</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3515-285-CM26</t>
+          <t>3693-105-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7143,12 +7143,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.061.700-5</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE EL QUISCO</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>POMPEYO CARRASCO SPA</t>
+          <t>GUILLERMO MORALES GROUP LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>81.318.700-0</t>
+          <t>78.027.627-4</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7173,7 +7173,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>39243.84</v>
+        <v>29726.08</v>
       </c>
     </row>
     <row r="111">
@@ -7301,7 +7301,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1456836-6-CM26</t>
+          <t>3624-359-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7326,12 +7326,12 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.981.410-K</t>
+          <t>69.060.600-3</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+          <t>I MUNICIPALIDAD DE NOGALES</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7341,12 +7341,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7356,13 +7356,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>25099.83</v>
+        <v>18595.48</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>1456836-7-CM26</t>
+          <t>2697-8-CM26</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.981.410-K</t>
+          <t>69.073.600-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA HANGA ROA</t>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7402,28 +7402,32 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>1422.6</v>
+        <v>72526.98</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>3624-359-CM26</t>
+          <t>377-310-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7438,22 +7442,22 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>69.060.600-3</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NOGALES</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7478,13 +7482,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>18595.48</v>
+        <v>22025.65</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2697-8-CM26</t>
+          <t>377-311-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7499,7 +7503,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -7509,12 +7513,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>69.073.600-4</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7524,32 +7528,28 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>79.649.970-2</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>72526.98</v>
+        <v>731.05</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>377-310-CM26</t>
+          <t>3820-637-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -7564,22 +7564,22 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>78.061.204-5</t>
         </is>
       </c>
       <c r="K117" t="inlineStr"/>
@@ -7604,13 +7604,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>22025.65</v>
+        <v>17210.12</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3820-637-CM26</t>
+          <t>3820-638-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7665,13 +7665,13 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>17210.12</v>
+        <v>397.75</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>3820-638-CM26</t>
+          <t>2688-237-CM26</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -7686,22 +7686,22 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.061.600-9</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7711,12 +7711,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K119" t="inlineStr"/>
@@ -7726,7 +7726,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>397.75</v>
+        <v>709.49</v>
       </c>
     </row>
     <row r="120">
@@ -7793,7 +7793,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2688-237-CM26</t>
+          <t>2780-248-CM26</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -7808,22 +7808,22 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>69.061.600-9</t>
+          <t>69.050.100-7</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+          <t>I MUNICIPALIDAD DE LA LIGUA</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>KOVACS SPA</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>80.522.900-4</t>
         </is>
       </c>
       <c r="K121" t="inlineStr"/>
@@ -7848,13 +7848,13 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>709.49</v>
+        <v>33566.81</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>1195104-212-CM26</t>
+          <t>1456835-12-CM26</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>62.000.920-2</t>
+          <t>61.981.430-4</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE MIGRACIONES</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL LITORAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -7909,13 +7909,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>26541.25</v>
+        <v>27051.14</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2780-248-CM26</t>
+          <t>640840-148-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7925,12 +7925,12 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.050.100-7</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA LIGUA</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>KOVACS SPA</t>
+          <t>H. Motores S.A.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>80.522.900-4</t>
+          <t>76.124.915-0</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>33566.81</v>
+        <v>37712.43</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>1456835-12-CM26</t>
+          <t>4844-60-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7991,22 +7991,22 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.981.430-4</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL LITORAL</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8031,13 +8031,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>27051.14</v>
+        <v>71799.47</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>640840-148-CM26</t>
+          <t>4844-61-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>H. Motores S.A.</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>76.124.915-0</t>
+          <t>76.027.979-k</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8092,13 +8092,13 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>37712.43</v>
+        <v>2964.74</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>4844-60-CM26</t>
+          <t>1048-342-CM26</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8108,17 +8108,17 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>71799.47</v>
+        <v>68076.10000000001</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4844-61-CM26</t>
+          <t>4803-226-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -8184,12 +8184,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>60.201.000-7</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>SENADO DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K127" t="inlineStr"/>
@@ -8214,7 +8214,190 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2964.74</v>
+        <v>36732.47</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>4803-227-CM26</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>60.201.000-7</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>SENADO DE LA REPUBLICA</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>76.296.863-0</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="n">
+        <v>931.28</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>3232-662-CM26</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>69.073.500-8</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="n">
+        <v>39349.29</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2694-228-CM26</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>69.073.600-4</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>H. Motores S.A.</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>76.124.915-0</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="n">
+        <v>34300.29</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
@@ -562,7 +562,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>96.545.450-0</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1464,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1529,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1655,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1720,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1785,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1850,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1915,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1980,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2045,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2110,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2175,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2240,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2305,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2370,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2435,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2500,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2565,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2630,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2760,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2825,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2827,7 +2955,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2888,7 +3020,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2949,7 +3085,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3010,7 +3150,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3071,7 +3215,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3132,7 +3280,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3193,7 +3345,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3254,7 +3410,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3315,7 +3475,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3376,7 +3540,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3437,7 +3605,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3498,7 +3670,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3559,7 +3735,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3620,7 +3800,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3742,7 +3926,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3803,7 +3991,11 @@
           <t>79.853.470-K</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3864,7 +4056,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3925,7 +4121,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3986,7 +4186,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4047,7 +4251,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4108,7 +4316,11 @@
           <t>96.928.530-4</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4169,7 +4381,11 @@
           <t>76.141.853-k</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4230,7 +4446,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4291,7 +4511,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4352,7 +4576,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4413,7 +4641,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4474,7 +4706,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4535,7 +4771,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4596,7 +4836,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4657,7 +4901,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4718,7 +4966,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4779,7 +5031,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4966,7 +5222,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5027,7 +5287,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5088,7 +5352,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5149,7 +5417,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5210,7 +5482,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5271,7 +5547,11 @@
           <t>78.098.600-K</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5332,7 +5612,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5393,7 +5677,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5454,7 +5742,11 @@
           <t>96.918.300-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5515,7 +5807,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5576,7 +5872,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5637,7 +5937,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5698,7 +6002,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5820,7 +6128,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5881,7 +6193,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6003,7 +6319,11 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6129,7 +6449,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6251,7 +6575,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6312,7 +6640,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6373,7 +6705,11 @@
           <t>84.807.200-1</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6434,7 +6770,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6495,7 +6835,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6617,7 +6961,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6739,7 +7087,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6800,7 +7152,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6861,7 +7217,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6922,7 +7282,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7044,7 +7408,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7105,7 +7473,11 @@
           <t>81.318.700-0</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7166,7 +7538,11 @@
           <t>78.027.627-4</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7349,7 +7725,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7475,7 +7855,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7536,7 +7920,11 @@
           <t>79.649.970-2</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7597,7 +7985,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7658,7 +8050,11 @@
           <t>78.061.204-5</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7841,7 +8237,11 @@
           <t>80.522.900-4</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7902,7 +8302,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7963,7 +8367,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8207,7 +8615,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8268,7 +8680,11 @@
           <t>76.296.863-0</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8329,7 +8745,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8390,7 +8810,11 @@
           <t>76.124.915-0</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
@@ -6514,7 +6514,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1607,7 +1607,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3138-17-CM25</t>
+          <t>3134-51-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.953.100-0</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1666,13 +1666,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>61000.99</v>
+        <v>31770.61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3134-51-CM25</t>
+          <t>3138-17-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.953.100-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>31770.61</v>
+        <v>61000.99</v>
       </c>
     </row>
     <row r="21">
@@ -2517,7 +2517,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>640840-82-CM25</t>
+          <t>3035-216-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.060.700-k</t>
+          <t>69.060.200-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUINTERO</t>
+          <t>I MUNICIPALIDAD DE LA CRUZ</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>79.649.970-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>27363.15</v>
+        <v>28143.53</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3035-216-CM25</t>
+          <t>1725-4794-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>69.060.200-8</t>
+          <t>60.901.002-9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CRUZ</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2622,17 +2622,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ SERVIMAQ SPA</t>
+          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>79.649.970-2</t>
+          <t>76.296.863-0</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2641,13 +2641,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>28143.53</v>
+        <v>233767.46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1725-4794-CM25</t>
+          <t>640840-82-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>60.901.002-9</t>
+          <t>69.060.700-k</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
+          <t>I MUNICIPALIDAD DE QUINTERO</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2687,17 +2687,17 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ PORTILLO SUR LTDA</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.296.863-0</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2706,7 +2706,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>233767.46</v>
+        <v>27363.15</v>
       </c>
     </row>
     <row r="36">
@@ -6856,7 +6856,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>1048-223-CM26</t>
+          <t>3561-226-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6876,17 +6876,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>69.073.700-0</t>
+          <t>69.060.300-4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EL TABO</t>
+          <t>I MUNICIPALIDAD DE LA CALERA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -6896,28 +6896,32 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>SUMMIT MOTORS S.A.</t>
+          <t>SUMMIT STORE SPA</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>76.027.979-k</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
+          <t>78.061.204-5</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>37270.54</v>
+        <v>18461.86</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>3561-226-CM26</t>
+          <t>1048-223-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6937,17 +6941,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.073.700-0</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE EL TABO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -6957,26 +6961,22 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SUMMIT STORE SPA</t>
+          <t>SUMMIT MOTORS S.A.</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>78.061.204-5</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.027.979-k</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>18461.86</v>
+        <v>37270.54</v>
       </c>
     </row>
     <row r="102">
@@ -7108,7 +7108,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3624-311-CM26</t>
+          <t>3624-312-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>AUTOMOTORES GILDEMEISTER SPA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>79.649.140-k</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -7167,13 +7167,13 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>26694.05</v>
+        <v>71659.32000000001</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3624-312-CM26</t>
+          <t>3624-311-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>71659.32000000001</v>
+        <v>26694.05</v>
       </c>
     </row>
     <row r="106">
@@ -7811,7 +7811,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>377-310-CM26</t>
+          <t>377-311-CM26</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -7870,13 +7870,13 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>22025.65</v>
+        <v>731.05</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>377-311-CM26</t>
+          <t>377-310-CM26</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>731.05</v>
+        <v>22025.65</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3820-637-CM26</t>
+          <t>3820-638-CM26</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8000,13 +8000,13 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>17210.12</v>
+        <v>397.75</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3820-638-CM26</t>
+          <t>3820-637-CM26</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>397.75</v>
+        <v>17210.12</v>
       </c>
     </row>
     <row r="119">
@@ -8388,7 +8388,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>4844-60-CM26</t>
+          <t>4844-61-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8443,13 +8443,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>71799.47</v>
+        <v>2964.74</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>4844-61-CM26</t>
+          <t>4844-60-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8504,7 +8504,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>2964.74</v>
+        <v>71799.47</v>
       </c>
     </row>
     <row r="126">
@@ -8571,7 +8571,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4803-226-CM26</t>
+          <t>4803-227-CM26</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8630,13 +8630,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>36732.47</v>
+        <v>931.28</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>4803-227-CM26</t>
+          <t>4803-226-CM26</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>931.28</v>
+        <v>36732.47</v>
       </c>
     </row>
     <row r="129">
@@ -8721,7 +8721,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -8826,6 +8826,457 @@
       </c>
       <c r="M130" s="2" t="n">
         <v>34300.29</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>4290-89-CM26</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>69.061.100-7</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="n">
+        <v>33867.16</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>4290-90-CM26</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>69.061.100-7</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LIMACHE</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2755-421-CM26</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>69.073.400-1</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>SKC Transportes S.A.</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>76.176.602-3</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="n">
+        <v>25441.77</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>643-256-CM26</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>61.817.000-4</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="n">
+        <v>51384.7</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>643-257-CM26</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>61.817.000-4</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION V REGION</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>KOVACS SPA</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>80.522.900-4</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="n">
+        <v>1527.68</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>377-467-CM26</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>69.061.600-9</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="n">
+        <v>813.42</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>377-466-CM26</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>69.061.600-9</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ALGARROBO</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>COMERCIAL AUTOMOTRIZ SPA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>96.928.530-4</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="n">
+        <v>65351.95</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/valparaiso.xlsx
@@ -8408,7 +8408,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
